--- a/artfynd/A 30737-2026 artfynd.xlsx
+++ b/artfynd/A 30737-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134236489</v>
+        <v>137544746</v>
       </c>
       <c r="B6" t="n">
-        <v>57776</v>
+        <v>9424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1119,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102118</v>
+        <v>101246</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oskarshamns kommun, Sm</t>
+          <t>Oskarshamns kommun, kraftnät, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596564</v>
+        <v>596728</v>
       </c>
       <c r="R6" t="n">
-        <v>6366308</v>
+        <v>6366237</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,17 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 individ, flög iväg.</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,22 +1202,22 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mathias Öster</t>
+          <t>Sofie Alveteg, Frida Sjöborg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134236489</t>
+          <t>https://artportalen.se/Sighting/137544746</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134236100</v>
+        <v>134236489</v>
       </c>
       <c r="B7" t="n">
-        <v>6290</v>
+        <v>57776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1225,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102351</v>
+        <v>102118</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymalus limbatus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oskarshamns kommun, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596936</v>
+        <v>596564</v>
       </c>
       <c r="R7" t="n">
-        <v>6366064</v>
+        <v>6366308</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,17 +1279,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hjälmflatbagge</t>
+          <t>1 individ, flög iväg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,7 +1298,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,22 +1309,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Molander</t>
+          <t>Mathias Öster</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134236100</t>
+          <t>https://artportalen.se/Sighting/134236489</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134236567</v>
+        <v>134236100</v>
       </c>
       <c r="B8" t="n">
-        <v>106236</v>
+        <v>6290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,34 +1332,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gullviva</t>
-        </is>
+        <v>102351</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thymalus limbatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oskarshamns kommun, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596424</v>
+        <v>596936</v>
       </c>
       <c r="R8" t="n">
-        <v>6366302</v>
+        <v>6366064</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,17 +1386,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>10-tal</t>
+          <t>Hjälmflatbagge</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,6 +1405,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1418,22 +1417,22 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hanna Bengtsson</t>
+          <t>Mikael Molander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134236567</t>
+          <t>https://artportalen.se/Sighting/134236100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134236570</v>
+        <v>137544427</v>
       </c>
       <c r="B9" t="n">
-        <v>106236</v>
+        <v>56958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,34 +1440,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>208257</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oskarshamns kommun, Sm</t>
+          <t>Oskarshamns kommun, kraftnät, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596717</v>
+        <v>596726</v>
       </c>
       <c r="R9" t="n">
-        <v>6366268</v>
+        <v>6366206</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,17 +1501,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3 plantor</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,6 +1515,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,16 +1533,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134236570</t>
+          <t>https://artportalen.se/Sighting/137544427</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134236582</v>
+        <v>137544429</v>
       </c>
       <c r="B10" t="n">
-        <v>106236</v>
+        <v>56958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,34 +1550,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>208257</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oskarshamns kommun, Sm</t>
+          <t>Oskarshamns kommun, kraftnät, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596856</v>
+        <v>596727</v>
       </c>
       <c r="R10" t="n">
-        <v>6365996</v>
+        <v>6366206</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1602,17 +1609,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>20-tal</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,22 +1634,22 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hanna Bengtsson</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134236582</t>
+          <t>https://artportalen.se/Sighting/137544429</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134236603</v>
+        <v>134236567</v>
       </c>
       <c r="B11" t="n">
-        <v>101403</v>
+        <v>106236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,21 +1657,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596405</v>
+        <v>596424</v>
       </c>
       <c r="R11" t="n">
-        <v>6366299</v>
+        <v>6366302</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1717,6 +1719,11 @@
           <t>2024-06-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10-tal</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1739,6 +1746,322 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236567</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134236570</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596717</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6366268</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3 plantor</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236570</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134236582</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596856</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6365996</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>20-tal</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236582</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134236603</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>596405</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6366299</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134236603</t>
         </is>
@@ -1756,6 +2079,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
